--- a/tests/testdata/excel/ファイル名/スペース 入り ブック.xlsx
+++ b/tests/testdata/excel/ファイル名/スペース 入り ブック.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{119C3EDF-28D5-4304-BE3C-73998952BD76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6C10790-7646-4D30-BF08-FDD27D5235D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="10515" xr2:uid="{54758B55-97B5-4077-9353-46978862504E}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{91BEB9B3-9439-43D3-B720-5204CB35C44E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05AB523B-83F1-4561-A8F8-A6B52AE5105C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC4A96A5-F0A5-41F2-8317-EF8D453353C3}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>

--- a/tests/testdata/excel/ファイル名/スペース 入り ブック.xlsx
+++ b/tests/testdata/excel/ファイル名/スペース 入り ブック.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6C10790-7646-4D30-BF08-FDD27D5235D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FA1F97D7-7571-4A94-AF5C-94137EE1A43F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{91BEB9B3-9439-43D3-B720-5204CB35C44E}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{A75B5BD5-359E-4BB4-8AD4-8EBAF068D4E9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC4A96A5-F0A5-41F2-8317-EF8D453353C3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C020475-8C15-44F3-9A1B-D01846CB25EA}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
